--- a/content/post/drafts/season-prediction/ladies_simple-model-tests-predicted_rmse.xlsx
+++ b/content/post/drafts/season-prediction/ladies_simple-model-tests-predicted_rmse.xlsx
@@ -59,10 +59,10 @@
     <t xml:space="preserve">Spline</t>
   </si>
   <si>
+    <t xml:space="preserve">XGBoost</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tobit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XGBoost</t>
   </si>
   <si>
     <t xml:space="preserve">Square Root</t>
@@ -610,25 +610,25 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>0.19545556155355</v>
+        <v>0.18428161751533</v>
       </c>
       <c r="C9" t="n">
-        <v>0.162300701110485</v>
+        <v>0.213415070006983</v>
       </c>
       <c r="D9" t="n">
-        <v>0.271909910609474</v>
+        <v>0.188946816178697</v>
       </c>
       <c r="E9" t="n">
-        <v>0.353505334194928</v>
+        <v>0.26579667311855</v>
       </c>
       <c r="F9" t="n">
-        <v>0.165175255235491</v>
+        <v>0.19300657956373</v>
       </c>
       <c r="G9" t="n">
-        <v>0.168614632613755</v>
+        <v>0.236089824081874</v>
       </c>
       <c r="H9" t="n">
-        <v>0.21949356588628</v>
+        <v>0.213589430077527</v>
       </c>
     </row>
     <row r="10">
@@ -636,25 +636,25 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>0.186150675512024</v>
+        <v>0.19545556155355</v>
       </c>
       <c r="C10" t="n">
-        <v>0.218469157872191</v>
+        <v>0.162300701110485</v>
       </c>
       <c r="D10" t="n">
-        <v>0.261475225697434</v>
+        <v>0.271909910609474</v>
       </c>
       <c r="E10" t="n">
-        <v>0.260379315312132</v>
+        <v>0.353505334194928</v>
       </c>
       <c r="F10" t="n">
-        <v>0.189840524033126</v>
+        <v>0.165175255235491</v>
       </c>
       <c r="G10" t="n">
-        <v>0.215903657364679</v>
+        <v>0.168614632613755</v>
       </c>
       <c r="H10" t="n">
-        <v>0.222036425965265</v>
+        <v>0.21949356588628</v>
       </c>
     </row>
     <row r="11">
